--- a/registration_forms/002_environmental_literacy_educator_cohort_registration_form--registration_forms.xlsx
+++ b/registration_forms/002_environmental_literacy_educator_cohort_registration_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1279,17 +1279,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>teaching_area_choices</t>
+          <t>teaching_level_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>natural_resources</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Natural Resources</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>beginner</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Beginner</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1318,29 +1318,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>teaching_level_choices</t>
+          <t>program_length_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>advanced</t>
+          <t>1_month</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Advanced</t>
+          <t>1 month</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1_month</t>
+          <t>2-3_months</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1 month</t>
+          <t>2-3 months</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2-3_months</t>
+          <t>6-9_months</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2-3 months</t>
+          <t>6-9 months</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6-9_months</t>
+          <t>1-2_years</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6-9 months</t>
+          <t>1-2 years</t>
         </is>
       </c>
     </row>
@@ -1403,29 +1403,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1-2_years</t>
+          <t>over_2_years</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1-2 years</t>
+          <t>Over 2 years</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>program_length_choices</t>
+          <t>target_audience_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>over_2_years</t>
+          <t>adults</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Over 2 years</t>
+          <t>Adults</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>adults</t>
+          <t>children</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Adults</t>
+          <t>Children</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>children</t>
+          <t>students</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Children</t>
+          <t>Students</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>students</t>
+          <t>teachers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Teachers</t>
         </is>
       </c>
     </row>
@@ -1488,29 +1488,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>teachers</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Teachers</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>target_audience_choices</t>
+          <t>language_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>english</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>spanish</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1556,29 +1556,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>french</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>language_choices</t>
+          <t>teaching_language_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>english</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>spanish</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1624,29 +1624,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>french</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>teaching_language_choices</t>
+          <t>submission_status_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Draft</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Submitted</t>
         </is>
       </c>
     </row>
@@ -1675,27 +1675,10 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>published</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
-        <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>submission_status_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
